--- a/NewYork.xlsx
+++ b/NewYork.xlsx
@@ -6032,18 +6032,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">

--- a/NewYork.xlsx
+++ b/NewYork.xlsx
@@ -59144,7 +59144,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T999"/>
   <sortState ref="A2:T789">
     <sortCondition ref="S2:S789"/>
   </sortState>
